--- a/reports/pdf_rolling5_20260805.xlsx
+++ b/reports/pdf_rolling5_20260805.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,001억   ·   현금 228억(5.2%)      오늘 2026-08-05  vs  5일전 2026-07-29      매수 13종목  /  매도 11종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,232억   ·   현금 228억(5.2%)      오늘 2026-08-05  vs  5일전 2026-07-29      매수 13종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>99</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>5190451200</v>
+        <v>5200588800</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-59</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-3739750400</v>
+        <v>-3747054600</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>92</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>886497280</v>
+        <v>888228720</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-46</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-420638720</v>
+        <v>-421460280</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>61</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1639680000</v>
+        <v>1642882500</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-27</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-3312230400</v>
+        <v>-3318699600</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>54</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>735436800</v>
+        <v>736873200</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-26</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-397230080</v>
+        <v>-398005920</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2192486400</v>
+        <v>2196768600</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-23</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-704204800</v>
+        <v>-705580200</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>33</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>3281203200</v>
+        <v>3287611800</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-18</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-591667200</v>
+        <v>-592822800</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>825344000</v>
+        <v>826956000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-17</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-2304819200</v>
+        <v>-2309320800</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1098240000</v>
+        <v>1100385000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>-11</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-231475200</v>
+        <v>-231927300</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1010,88 +1010,88 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>788940800</v>
+        <v>5204898000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>2.01%→2.18%</t>
+          <t>4.63%→4.98%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>197→216</t>
+          <t>56→75</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-2362368000</v>
+        <v>-2874852000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>4.61%→3.63%</t>
+          <t>1.68%→1.04%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>44→38</t>
+          <t>15→9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>5194752000</v>
+        <v>790481700</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>4.63%→4.98%</t>
+          <t>2.01%→2.18%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>56→75</t>
+          <t>197→216</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-2869248000</v>
+        <v>-2366982000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>1.68%→1.04%</t>
+          <t>4.61%→3.63%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>15→9</t>
+          <t>44→38</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
         <v>8</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>891289600</v>
+        <v>893030400</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>-4</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-198246400</v>
+        <v>-198633600</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>7</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>178124800</v>
+        <v>178472700</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1190400000</v>
+        <v>1192725000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,369억   ·   현금 28억(0.7%)      오늘 2026-08-05  vs  5일전 2026-07-29      매수 2종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,729억   ·   현금 28억(0.7%)      오늘 2026-08-05  vs  5일전 2026-07-29      매수 2종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -1294,7 +1294,7 @@
         <v>45</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>6295860000</v>
+        <v>6283845000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>-21</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-2044543200</v>
+        <v>-2040641400</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>5</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>3867120000</v>
+        <v>3859740000</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,208억   ·   현금 99억(4.1%)      오늘 2026-08-05  vs  5일전 2026-07-29      매수 4종목  /  매도 4종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,367억   ·   현금 99억(4.1%)      오늘 2026-08-05  vs  5일전 2026-07-29      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -1455,7 +1455,7 @@
         <v>142</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>5002035200</v>
+        <v>4980224000</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>-41</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-1655809600</v>
+        <v>-1648589500</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>50</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>3340240000</v>
+        <v>3325675000</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>-17</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-4497112000</v>
+        <v>-4477502500</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>36</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1533139200</v>
+        <v>1526454000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>-10</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-1599600000</v>
+        <v>-1592625000</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>19</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>874516800</v>
+        <v>870703500</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>-7</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-654976000</v>
+        <v>-652120000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,992억   ·   현금 27억(1.2%)      오늘 2026-08-05  vs  5일전 2026-07-29      매수 5종목  /  매도 3종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,168억   ·   현금 27억(1.2%)      오늘 2026-08-05  vs  5일전 2026-07-29      매수 5종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
@@ -1901,7 +1901,7 @@
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 243억   ·   현금 14억(5.5%)      오늘 2026-08-05  vs  5일전 2026-07-29      매수 6종목  /  매도 6종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 261억   ·   현금 14억(5.1%)      오늘 2026-08-05  vs  5일전 2026-07-29      매수 6종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B43" s="4" t="n"/>
@@ -1997,11 +1997,11 @@
         <v>59</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>120581250</v>
+        <v>120138750</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>2.41%→2.91%</t>
+          <t>2.23%→2.69%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -2018,11 +2018,11 @@
         <v>-145</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-38171250</v>
+        <v>-40128750</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>2.90%→2.72%</t>
+          <t>2.83%→2.66%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -2041,11 +2041,11 @@
         <v>33</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>82046250</v>
+        <v>91080000</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>7.05%→7.34%</t>
+          <t>7.26%→7.57%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -2062,11 +2062,11 @@
         <v>-98</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-76807500</v>
+        <v>-91581000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>1.80%→1.46%</t>
+          <t>1.99%→1.62%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -2085,11 +2085,11 @@
         <v>15</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>72000000</v>
+        <v>75262500</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>3.43%→3.71%</t>
+          <t>3.32%→3.60%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2106,11 +2106,11 @@
         <v>-91</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-48525750</v>
+        <v>-52552500</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>1.06%→0.84%</t>
+          <t>1.06%→0.85%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2129,11 +2129,11 @@
         <v>11</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>53542500</v>
+        <v>55770000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>1.76%→1.97%</t>
+          <t>1.70%→1.91%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2150,11 +2150,11 @@
         <v>-22</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-26383500</v>
+        <v>-32488500</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>2.73%→2.60%</t>
+          <t>3.12%→2.98%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
@@ -2173,11 +2173,11 @@
         <v>10</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>94125000</v>
+        <v>94500000</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>2.88%→3.26%</t>
+          <t>2.68%→3.04%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2194,11 +2194,11 @@
         <v>-14</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-25515000</v>
+        <v>-30030000</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>6.27%→6.12%</t>
+          <t>6.85%→6.69%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
@@ -2217,11 +2217,11 @@
         <v>6</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>42165000</v>
+        <v>43425000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>2.66%→2.82%</t>
+          <t>2.54%→2.70%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -2238,11 +2238,11 @@
         <v>-6</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-105975000</v>
+        <v>-113400000</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>1.80%→1.34%</t>
+          <t>1.79%→1.33%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
@@ -2254,7 +2254,7 @@
     <row r="53" ht="19" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 456억   ·   현금 26억(4.8%)      오늘 2026-08-05  vs  5일전 2026-07-29      매수 5종목  /  매도 3종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 501억   ·   현금 25억(4.8%)      오늘 2026-08-05  vs  5일전 2026-07-29      매수 5종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B53" s="4" t="n"/>
@@ -2350,7 +2350,7 @@
         <v>124</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>899942400</v>
+        <v>867801600</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>-34</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-707526400</v>
+        <v>-682257600</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>62</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>558297600</v>
+        <v>538358400</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>-9</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-387576000</v>
+        <v>-373734000</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>24</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>717696000</v>
+        <v>692064000</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>-7</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-1214416000</v>
+        <v>-1171044000</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>21</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>258484800</v>
+        <v>249253200</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>16</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>214681600</v>
+        <v>207014400</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260805.xlsx
+++ b/reports/pdf_rolling5_20260805.xlsx
@@ -1010,88 +1010,88 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>5204898000</v>
+        <v>790481700</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>4.63%→4.98%</t>
+          <t>2.01%→2.18%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>56→75</t>
+          <t>197→216</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-2874852000</v>
+        <v>-2366982000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>1.68%→1.04%</t>
+          <t>4.61%→3.63%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>15→9</t>
+          <t>44→38</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>790481700</v>
+        <v>5204898000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>2.01%→2.18%</t>
+          <t>4.63%→4.98%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>197→216</t>
+          <t>56→75</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-2366982000</v>
+        <v>-2874852000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>4.61%→3.63%</t>
+          <t>1.68%→1.04%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>44→38</t>
+          <t>15→9</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260805.xlsx
+++ b/reports/pdf_rolling5_20260805.xlsx
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>790481700</v>
+        <v>5204898000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>2.01%→2.18%</t>
+          <t>4.63%→4.98%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>197→216</t>
+          <t>56→75</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1054,23 +1054,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>5204898000</v>
+        <v>790481700</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>4.63%→4.98%</t>
+          <t>2.01%→2.18%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>56→75</t>
+          <t>197→216</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
